--- a/test/hl_test.xlsx
+++ b/test/hl_test.xlsx
@@ -5139,2058 +5139,2595 @@
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7">
-        <v>646.9</v>
-      </c>
-      <c r="C2" s="9">
-        <v>628.5</v>
+      <c r="B2" s="8">
+        <v>459.75</v>
+      </c>
+      <c r="C2" s="10">
+        <v>445.85</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="4"/>
+      <c r="F2" s="15">
+        <v>646.9</v>
+      </c>
+      <c r="G2" s="4">
+        <v>628.5</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19">
-        <v>5789.8</v>
-      </c>
-      <c r="C3" s="20">
-        <v>5585.5</v>
+      <c r="B3" s="8">
+        <v>7520</v>
+      </c>
+      <c r="C3" s="10">
+        <v>7340.7</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="5"/>
+      <c r="F3" s="16">
+        <v>5789.8</v>
+      </c>
+      <c r="G3" s="5">
+        <v>5585.5</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="8">
-        <v>174.3</v>
+        <v>196.17</v>
       </c>
       <c r="C4" s="10">
-        <v>169.25</v>
+        <v>193.05</v>
       </c>
       <c r="D4" s="13"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="5"/>
+      <c r="F4" s="16">
+        <v>174.3</v>
+      </c>
+      <c r="G4" s="5">
+        <v>169.25</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="8">
-        <v>212.65</v>
+        <v>319.5</v>
       </c>
       <c r="C5" s="10">
-        <v>201</v>
+        <v>308.60000000000002</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="5"/>
+      <c r="F5" s="16">
+        <v>212.65</v>
+      </c>
+      <c r="G5" s="5">
+        <v>201</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="19">
-        <v>3143.4</v>
-      </c>
-      <c r="C6" s="20">
-        <v>3061.25</v>
+      <c r="B6" s="8">
+        <v>2526.3000000000002</v>
+      </c>
+      <c r="C6" s="10">
+        <v>2400</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="5"/>
+      <c r="F6" s="16">
+        <v>3143.4</v>
+      </c>
+      <c r="G6" s="5">
+        <v>3061.25</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="19">
-        <v>1288.8499999999999</v>
-      </c>
-      <c r="C7" s="20">
-        <v>1256.6500000000001</v>
+      <c r="B7" s="8">
+        <v>1226.9000000000001</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1163.1500000000001</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="5"/>
+      <c r="F7" s="16">
+        <v>1288.8499999999999</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1256.6500000000001</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="19">
-        <v>6233</v>
-      </c>
-      <c r="C8" s="20">
-        <v>6109.7</v>
+      <c r="B8" s="8">
+        <v>5492.5</v>
+      </c>
+      <c r="C8" s="10">
+        <v>5418.85</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="5"/>
+      <c r="F8" s="16">
+        <v>6233</v>
+      </c>
+      <c r="G8" s="5">
+        <v>6109.7</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="8">
-        <v>592.79999999999995</v>
+        <v>522.54999999999995</v>
       </c>
       <c r="C9" s="10">
-        <v>583.04999999999995</v>
+        <v>510.65</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="5"/>
+      <c r="F9" s="16">
+        <v>592.79999999999995</v>
+      </c>
+      <c r="G9" s="5">
+        <v>583.04999999999995</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="19">
-        <v>7018.95</v>
-      </c>
-      <c r="C10" s="20">
-        <v>6930.1</v>
+      <c r="B10" s="8">
+        <v>7030</v>
+      </c>
+      <c r="C10" s="10">
+        <v>6816</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="5"/>
+      <c r="F10" s="16">
+        <v>7018.95</v>
+      </c>
+      <c r="G10" s="5">
+        <v>6930.1</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="8">
-        <v>503.35</v>
+        <v>515</v>
       </c>
       <c r="C11" s="10">
-        <v>470.7</v>
+        <v>506.1</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="5"/>
+      <c r="F11" s="16">
+        <v>503.35</v>
+      </c>
+      <c r="G11" s="5">
+        <v>470.7</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="8">
-        <v>164.85</v>
+        <v>237.06</v>
       </c>
       <c r="C12" s="10">
-        <v>160.25</v>
+        <v>230.36</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="5"/>
+      <c r="F12" s="16">
+        <v>164.85</v>
+      </c>
+      <c r="G12" s="5">
+        <v>160.25</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="19">
-        <v>2057.4</v>
-      </c>
-      <c r="C13" s="20">
-        <v>1956.8</v>
+      <c r="B13" s="8">
+        <v>1850</v>
+      </c>
+      <c r="C13" s="10">
+        <v>1792.95</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="5"/>
+      <c r="F13" s="16">
+        <v>2057.4</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1956.8</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="19">
-        <v>6060</v>
-      </c>
-      <c r="C14" s="20">
-        <v>5932.15</v>
+      <c r="B14" s="8">
+        <v>7412.4</v>
+      </c>
+      <c r="C14" s="10">
+        <v>7200.6</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="5"/>
+      <c r="F14" s="16">
+        <v>6060</v>
+      </c>
+      <c r="G14" s="5">
+        <v>5932.15</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="8">
-        <v>587.29999999999995</v>
+        <v>593</v>
       </c>
       <c r="C15" s="10">
-        <v>575.1</v>
+        <v>584.70000000000005</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="5"/>
+      <c r="F15" s="16">
+        <v>587.29999999999995</v>
+      </c>
+      <c r="G15" s="5">
+        <v>575.1</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="19">
-        <v>1015.8</v>
-      </c>
-      <c r="C16" s="20">
-        <v>984.3</v>
+      <c r="B16" s="8">
+        <v>1244</v>
+      </c>
+      <c r="C16" s="10">
+        <v>1220.75</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="5"/>
+      <c r="F16" s="16">
+        <v>1015.8</v>
+      </c>
+      <c r="G16" s="5">
+        <v>984.3</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="19">
-        <v>1589.6</v>
-      </c>
-      <c r="C17" s="20">
-        <v>1547.5</v>
+      <c r="B17" s="8">
+        <v>9272.4</v>
+      </c>
+      <c r="C17" s="10">
+        <v>8992.25</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="5"/>
+      <c r="F17" s="16">
+        <v>1589.6</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1547.5</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="19">
-        <v>6578</v>
-      </c>
-      <c r="C18" s="20">
-        <v>6360</v>
+      <c r="B18" s="8">
+        <v>1610.05</v>
+      </c>
+      <c r="C18" s="10">
+        <v>1567.65</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="5"/>
+      <c r="F18" s="16">
+        <v>6578</v>
+      </c>
+      <c r="G18" s="5">
+        <v>6360</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="19">
-        <v>2286.15</v>
-      </c>
-      <c r="C19" s="20">
-        <v>2233</v>
+      <c r="B19" s="8">
+        <v>6726.25</v>
+      </c>
+      <c r="C19" s="10">
+        <v>6495</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="5"/>
+      <c r="F19" s="16">
+        <v>2286.15</v>
+      </c>
+      <c r="G19" s="5">
+        <v>2233</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="8">
-        <v>361.95</v>
+        <v>2760.65</v>
       </c>
       <c r="C20" s="10">
-        <v>350</v>
+        <v>2688</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="5"/>
+      <c r="F20" s="16">
+        <v>361.95</v>
+      </c>
+      <c r="G20" s="5">
+        <v>350</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="8">
-        <v>186</v>
+        <v>571.95000000000005</v>
       </c>
       <c r="C21" s="10">
-        <v>179.1</v>
+        <v>550.35</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="5"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="5"/>
+      <c r="F21" s="16">
+        <v>186</v>
+      </c>
+      <c r="G21" s="5">
+        <v>179.1</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="8">
-        <v>261.5</v>
+        <v>174.07</v>
       </c>
       <c r="C22" s="10">
-        <v>250.15</v>
+        <v>170.3</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="5"/>
+      <c r="F22" s="16">
+        <v>261.5</v>
+      </c>
+      <c r="G22" s="5">
+        <v>250.15</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="8">
-        <v>1418.85</v>
+        <v>252</v>
       </c>
       <c r="C23" s="10">
-        <v>1386.45</v>
+        <v>245.6</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="5"/>
+      <c r="F23" s="16">
+        <v>1418.85</v>
+      </c>
+      <c r="G23" s="5">
+        <v>1386.45</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="8">
-        <v>196.75</v>
+        <v>1384.05</v>
       </c>
       <c r="C24" s="10">
-        <v>179.1</v>
+        <v>1355</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="5"/>
+      <c r="F24" s="16">
+        <v>196.75</v>
+      </c>
+      <c r="G24" s="5">
+        <v>179.1</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B25" s="8">
-        <v>1130.6500000000001</v>
+        <v>309.5</v>
       </c>
       <c r="C25" s="10">
-        <v>1099.0999999999999</v>
+        <v>304.35000000000002</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="5"/>
+      <c r="F25" s="16">
+        <v>1130.6500000000001</v>
+      </c>
+      <c r="G25" s="5">
+        <v>1099.0999999999999</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B26" s="8">
-        <v>227.7</v>
+        <v>1360.3</v>
       </c>
       <c r="C26" s="10">
-        <v>207.1</v>
+        <v>1316.85</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="5"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="5"/>
+      <c r="F26" s="16">
+        <v>227.7</v>
+      </c>
+      <c r="G26" s="5">
+        <v>207.1</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B27" s="8">
-        <v>262.60000000000002</v>
+        <v>253.8</v>
       </c>
       <c r="C27" s="10">
-        <v>250.25</v>
+        <v>247.66</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="5"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="5"/>
+      <c r="F27" s="16">
+        <v>262.60000000000002</v>
+      </c>
+      <c r="G27" s="5">
+        <v>250.25</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B28" s="8">
-        <v>5008.7</v>
+        <v>366.65</v>
       </c>
       <c r="C28" s="10">
-        <v>4912</v>
+        <v>358.05</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="5"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="5"/>
+      <c r="F28" s="16">
+        <v>5008.7</v>
+      </c>
+      <c r="G28" s="5">
+        <v>4912</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B29" s="8">
-        <v>760.5</v>
+        <v>5012.55</v>
       </c>
       <c r="C29" s="10">
-        <v>735.05</v>
+        <v>4891.1499999999996</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="5"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="5"/>
+      <c r="F29" s="16">
+        <v>760.5</v>
+      </c>
+      <c r="G29" s="5">
+        <v>735.05</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B30" s="8">
-        <v>554</v>
+        <v>602.6</v>
       </c>
       <c r="C30" s="10">
-        <v>529.75</v>
+        <v>589.4</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="5"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="5"/>
+      <c r="F30" s="16">
+        <v>554</v>
+      </c>
+      <c r="G30" s="5">
+        <v>529.75</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B31" s="8">
-        <v>734.35</v>
+        <v>103.42</v>
       </c>
       <c r="C31" s="10">
-        <v>709.15</v>
+        <v>101.86</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="5"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="5"/>
+      <c r="F31" s="16">
+        <v>734.35</v>
+      </c>
+      <c r="G31" s="5">
+        <v>709.15</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B32" s="8">
-        <v>350.9</v>
+        <v>835</v>
       </c>
       <c r="C32" s="10">
-        <v>339.5</v>
+        <v>818.05</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="5"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="5"/>
+      <c r="F32" s="16">
+        <v>350.9</v>
+      </c>
+      <c r="G32" s="5">
+        <v>339.5</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B33" s="8">
-        <v>1086</v>
+        <v>504.8</v>
       </c>
       <c r="C33" s="10">
-        <v>1055.6500000000001</v>
+        <v>492.05</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="5"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="5"/>
+      <c r="F33" s="16">
+        <v>1086</v>
+      </c>
+      <c r="G33" s="5">
+        <v>1055.6500000000001</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="8">
-        <v>1496.2</v>
-      </c>
-      <c r="C34" s="10">
-        <v>1466.05</v>
+      <c r="B34" s="19">
+        <v>1284.4000000000001</v>
+      </c>
+      <c r="C34" s="20">
+        <v>1258.5</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="5"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="5"/>
+      <c r="F34" s="16">
+        <v>1496.2</v>
+      </c>
+      <c r="G34" s="5">
+        <v>1466.05</v>
+      </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B35" s="8">
-        <v>6137.35</v>
+        <v>1505</v>
       </c>
       <c r="C35" s="10">
-        <v>6008.3</v>
+        <v>1473.9</v>
       </c>
       <c r="D35" s="13"/>
       <c r="E35" s="5"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="5"/>
+      <c r="F35" s="16">
+        <v>6137.35</v>
+      </c>
+      <c r="G35" s="5">
+        <v>6008.3</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B36" s="8">
-        <v>872.4</v>
+        <v>8689.9500000000007</v>
       </c>
       <c r="C36" s="10">
-        <v>845</v>
+        <v>8604.15</v>
       </c>
       <c r="D36" s="13"/>
       <c r="E36" s="5"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="5"/>
+      <c r="F36" s="16">
+        <v>872.4</v>
+      </c>
+      <c r="G36" s="5">
+        <v>845</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B37" s="8">
-        <v>1110</v>
+        <v>825.5</v>
       </c>
       <c r="C37" s="10">
-        <v>1059.75</v>
+        <v>810.05</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="5"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="5"/>
+      <c r="F37" s="16">
+        <v>1110</v>
+      </c>
+      <c r="G37" s="5">
+        <v>1059.75</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B38" s="8">
-        <v>285.8</v>
+        <v>1774.95</v>
       </c>
       <c r="C38" s="10">
-        <v>274.35000000000002</v>
+        <v>1745.4</v>
       </c>
       <c r="D38" s="13"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="5"/>
+      <c r="F38" s="16">
+        <v>285.8</v>
+      </c>
+      <c r="G38" s="5">
+        <v>274.35000000000002</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B39" s="8">
-        <v>2737.1</v>
+        <v>411.7</v>
       </c>
       <c r="C39" s="10">
-        <v>2678.5</v>
+        <v>405</v>
       </c>
       <c r="D39" s="13"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="5"/>
+      <c r="F39" s="16">
+        <v>2737.1</v>
+      </c>
+      <c r="G39" s="5">
+        <v>2678.5</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B40" s="8">
-        <v>530.35</v>
+        <v>3513.7</v>
       </c>
       <c r="C40" s="10">
-        <v>524.25</v>
+        <v>3439.05</v>
       </c>
       <c r="D40" s="13"/>
       <c r="E40" s="5"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="5"/>
+      <c r="F40" s="16">
+        <v>530.35</v>
+      </c>
+      <c r="G40" s="5">
+        <v>524.25</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B41" s="8">
-        <v>1893.9</v>
+        <v>534.35</v>
       </c>
       <c r="C41" s="10">
-        <v>1854.7</v>
+        <v>524</v>
       </c>
       <c r="D41" s="13"/>
       <c r="E41" s="5"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="5"/>
+      <c r="F41" s="16">
+        <v>1893.9</v>
+      </c>
+      <c r="G41" s="5">
+        <v>1854.7</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B42" s="8">
-        <v>495.5</v>
+        <v>1845.15</v>
       </c>
       <c r="C42" s="10">
-        <v>466.1</v>
+        <v>1809</v>
       </c>
       <c r="D42" s="13"/>
       <c r="E42" s="5"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="5"/>
+      <c r="F42" s="16">
+        <v>495.5</v>
+      </c>
+      <c r="G42" s="5">
+        <v>466.1</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B43" s="8">
-        <v>2123.5500000000002</v>
+        <v>1373.95</v>
       </c>
       <c r="C43" s="10">
-        <v>2080</v>
+        <v>1322.05</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="5"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="5"/>
+      <c r="F43" s="16">
+        <v>2123.5500000000002</v>
+      </c>
+      <c r="G43" s="5">
+        <v>2080</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B44" s="8">
-        <v>127.7</v>
+        <v>2743.75</v>
       </c>
       <c r="C44" s="10">
-        <v>122.75</v>
+        <v>2696.05</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="5"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="5"/>
+      <c r="F44" s="16">
+        <v>127.7</v>
+      </c>
+      <c r="G44" s="5">
+        <v>122.75</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B45" s="8">
-        <v>3524.7</v>
+        <v>118.1</v>
       </c>
       <c r="C45" s="10">
-        <v>3455.05</v>
+        <v>115.14</v>
       </c>
       <c r="D45" s="13"/>
       <c r="E45" s="5"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="5"/>
+      <c r="F45" s="16">
+        <v>3524.7</v>
+      </c>
+      <c r="G45" s="5">
+        <v>3455.05</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B46" s="8">
-        <v>6979.95</v>
+        <v>6022.8</v>
       </c>
       <c r="C46" s="10">
-        <v>6722</v>
+        <v>5902.1</v>
       </c>
       <c r="D46" s="13"/>
       <c r="E46" s="5"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="5"/>
+      <c r="F46" s="16">
+        <v>6979.95</v>
+      </c>
+      <c r="G46" s="5">
+        <v>6722</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B47" s="8">
-        <v>848.75</v>
+        <v>15980</v>
       </c>
       <c r="C47" s="10">
-        <v>809.3</v>
+        <v>15533.8</v>
       </c>
       <c r="D47" s="13"/>
       <c r="E47" s="5"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="5"/>
+      <c r="F47" s="16">
+        <v>848.75</v>
+      </c>
+      <c r="G47" s="5">
+        <v>809.3</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B48" s="8">
-        <v>6308.55</v>
+        <v>826.4</v>
       </c>
       <c r="C48" s="10">
-        <v>6214.5</v>
+        <v>808.95</v>
       </c>
       <c r="D48" s="13"/>
       <c r="E48" s="5"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="5"/>
+      <c r="F48" s="16">
+        <v>6308.55</v>
+      </c>
+      <c r="G48" s="5">
+        <v>6214.5</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B49" s="8">
-        <v>2773.95</v>
+        <v>1209.9000000000001</v>
       </c>
       <c r="C49" s="10">
-        <v>2682.5</v>
+        <v>1188.45</v>
       </c>
       <c r="D49" s="13"/>
       <c r="E49" s="5"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="5"/>
+      <c r="F49" s="16">
+        <v>2773.95</v>
+      </c>
+      <c r="G49" s="5">
+        <v>2682.5</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B50" s="8">
-        <v>306.8</v>
+        <v>3615.1</v>
       </c>
       <c r="C50" s="10">
-        <v>298.85000000000002</v>
+        <v>3492.4</v>
       </c>
       <c r="D50" s="13"/>
       <c r="E50" s="5"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="5"/>
+      <c r="F50" s="16">
+        <v>306.8</v>
+      </c>
+      <c r="G50" s="5">
+        <v>298.85000000000002</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B51" s="8">
-        <v>943.85</v>
+        <v>459.9</v>
       </c>
       <c r="C51" s="10">
-        <v>912.05</v>
+        <v>442</v>
       </c>
       <c r="D51" s="13"/>
       <c r="E51" s="5"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="5"/>
+      <c r="F51" s="16">
+        <v>943.85</v>
+      </c>
+      <c r="G51" s="5">
+        <v>912.05</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>56</v>
       </c>
       <c r="B52" s="8">
-        <v>752</v>
+        <v>1533.85</v>
       </c>
       <c r="C52" s="10">
-        <v>715.6</v>
+        <v>1491.8</v>
       </c>
       <c r="D52" s="13"/>
       <c r="E52" s="5"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="5"/>
+      <c r="F52" s="16">
+        <v>752</v>
+      </c>
+      <c r="G52" s="5">
+        <v>715.6</v>
+      </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>57</v>
       </c>
       <c r="B53" s="8">
-        <v>630.9</v>
+        <v>1092.5999999999999</v>
       </c>
       <c r="C53" s="10">
-        <v>606</v>
+        <v>1068.2</v>
       </c>
       <c r="D53" s="13"/>
       <c r="E53" s="5"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="5"/>
+      <c r="F53" s="16">
+        <v>630.9</v>
+      </c>
+      <c r="G53" s="5">
+        <v>606</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>58</v>
       </c>
       <c r="B54" s="8">
-        <v>1223.8</v>
+        <v>617.4</v>
       </c>
       <c r="C54" s="10">
-        <v>1203.7</v>
+        <v>597.04999999999995</v>
       </c>
       <c r="D54" s="13"/>
       <c r="E54" s="5"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="5"/>
+      <c r="F54" s="16">
+        <v>1223.8</v>
+      </c>
+      <c r="G54" s="5">
+        <v>1203.7</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B55" s="8">
-        <v>2234.1999999999998</v>
+        <v>1281.9000000000001</v>
       </c>
       <c r="C55" s="10">
-        <v>2157.9499999999998</v>
+        <v>1243.95</v>
       </c>
       <c r="D55" s="13"/>
       <c r="E55" s="5"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="5"/>
+      <c r="F55" s="16">
+        <v>2234.1999999999998</v>
+      </c>
+      <c r="G55" s="5">
+        <v>2157.9499999999998</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B56" s="8">
-        <v>424.85</v>
+        <v>2903.15</v>
       </c>
       <c r="C56" s="10">
-        <v>410.4</v>
+        <v>2779.15</v>
       </c>
       <c r="D56" s="13"/>
       <c r="E56" s="5"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="5"/>
+      <c r="F56" s="16">
+        <v>424.85</v>
+      </c>
+      <c r="G56" s="5">
+        <v>410.4</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>61</v>
       </c>
       <c r="B57" s="8">
-        <v>2208.9</v>
+        <v>587.79999999999995</v>
       </c>
       <c r="C57" s="10">
-        <v>2165.0500000000002</v>
+        <v>573.5</v>
       </c>
       <c r="D57" s="13"/>
       <c r="E57" s="5"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="5"/>
+      <c r="F57" s="16">
+        <v>2208.9</v>
+      </c>
+      <c r="G57" s="5">
+        <v>2165.0500000000002</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>62</v>
       </c>
       <c r="B58" s="8">
-        <v>546.95000000000005</v>
+        <v>2635.95</v>
       </c>
       <c r="C58" s="10">
-        <v>528.54999999999995</v>
+        <v>2554.0500000000002</v>
       </c>
       <c r="D58" s="13"/>
       <c r="E58" s="5"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="5"/>
+      <c r="F58" s="16">
+        <v>546.95000000000005</v>
+      </c>
+      <c r="G58" s="5">
+        <v>528.54999999999995</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B59" s="8">
-        <v>3182.55</v>
+        <v>476</v>
       </c>
       <c r="C59" s="10">
-        <v>3006</v>
+        <v>470.4</v>
       </c>
       <c r="D59" s="13"/>
       <c r="E59" s="5"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="5"/>
+      <c r="F59" s="16">
+        <v>3182.55</v>
+      </c>
+      <c r="G59" s="5">
+        <v>3006</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B60" s="8">
-        <v>1520.3</v>
+        <v>4529.5</v>
       </c>
       <c r="C60" s="10">
-        <v>1476.05</v>
+        <v>4451.25</v>
       </c>
       <c r="D60" s="13"/>
       <c r="E60" s="5"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="5"/>
+      <c r="F60" s="16">
+        <v>1520.3</v>
+      </c>
+      <c r="G60" s="5">
+        <v>1476.05</v>
+      </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>65</v>
       </c>
       <c r="B61" s="8">
-        <v>1677</v>
+        <v>1742.4</v>
       </c>
       <c r="C61" s="10">
-        <v>1642.85</v>
+        <v>1707.9</v>
       </c>
       <c r="D61" s="13"/>
       <c r="E61" s="5"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="5"/>
+      <c r="F61" s="16">
+        <v>1677</v>
+      </c>
+      <c r="G61" s="5">
+        <v>1642.85</v>
+      </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B62" s="8">
-        <v>3831.45</v>
+        <v>1900.5</v>
       </c>
       <c r="C62" s="10">
-        <v>3680</v>
+        <v>1835</v>
       </c>
       <c r="D62" s="13"/>
       <c r="E62" s="5"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="5"/>
+      <c r="F62" s="16">
+        <v>3831.45</v>
+      </c>
+      <c r="G62" s="5">
+        <v>3680</v>
+      </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B63" s="8">
-        <v>634.79999999999995</v>
+        <v>4279.3999999999996</v>
       </c>
       <c r="C63" s="10">
-        <v>611.29999999999995</v>
+        <v>4187</v>
       </c>
       <c r="D63" s="13"/>
       <c r="E63" s="5"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="5"/>
+      <c r="F63" s="16">
+        <v>634.79999999999995</v>
+      </c>
+      <c r="G63" s="5">
+        <v>611.29999999999995</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B64" s="8">
-        <v>534.04999999999995</v>
+        <v>690.15</v>
       </c>
       <c r="C64" s="10">
-        <v>517.5</v>
+        <v>638.65</v>
       </c>
       <c r="D64" s="13"/>
       <c r="E64" s="5"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="5"/>
+      <c r="F64" s="16">
+        <v>534.04999999999995</v>
+      </c>
+      <c r="G64" s="5">
+        <v>517.5</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B65" s="8">
-        <v>275.60000000000002</v>
+        <v>663.15</v>
       </c>
       <c r="C65" s="10">
-        <v>255.75</v>
+        <v>647.6</v>
       </c>
       <c r="D65" s="13"/>
       <c r="E65" s="5"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="5"/>
+      <c r="F65" s="16">
+        <v>275.60000000000002</v>
+      </c>
+      <c r="G65" s="5">
+        <v>255.75</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B66" s="19">
-        <v>1688.75</v>
-      </c>
-      <c r="C66" s="20">
-        <v>1633.05</v>
+      <c r="B66" s="8">
+        <v>281.14999999999998</v>
+      </c>
+      <c r="C66" s="10">
+        <v>273.25</v>
       </c>
       <c r="D66" s="13"/>
       <c r="E66" s="5"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="5"/>
+      <c r="F66" s="16">
+        <v>1688.75</v>
+      </c>
+      <c r="G66" s="5">
+        <v>1633.05</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B67" s="8">
-        <v>579</v>
+        <v>1888.8</v>
       </c>
       <c r="C67" s="10">
-        <v>563</v>
+        <v>1849.5</v>
       </c>
       <c r="D67" s="13"/>
       <c r="E67" s="5"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="5"/>
+      <c r="F67" s="16">
+        <v>579</v>
+      </c>
+      <c r="G67" s="5">
+        <v>563</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B68" s="8">
-        <v>138.25</v>
+        <v>695.5</v>
       </c>
       <c r="C68" s="10">
-        <v>133.4</v>
+        <v>667.7</v>
       </c>
       <c r="D68" s="13"/>
       <c r="E68" s="5"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="5"/>
+      <c r="F68" s="16">
+        <v>138.25</v>
+      </c>
+      <c r="G68" s="5">
+        <v>133.4</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B69" s="8">
-        <v>414</v>
+        <v>176.5</v>
       </c>
       <c r="C69" s="10">
-        <v>404</v>
+        <v>171.7</v>
       </c>
       <c r="D69" s="13"/>
       <c r="E69" s="5"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="5"/>
+      <c r="F69" s="16">
+        <v>414</v>
+      </c>
+      <c r="G69" s="5">
+        <v>404</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B70" s="8">
-        <v>565.9</v>
+        <v>324.60000000000002</v>
       </c>
       <c r="C70" s="10">
-        <v>549.95000000000005</v>
+        <v>317.8</v>
       </c>
       <c r="D70" s="13"/>
       <c r="E70" s="5"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="5"/>
+      <c r="F70" s="16">
+        <v>565.9</v>
+      </c>
+      <c r="G70" s="5">
+        <v>549.95000000000005</v>
+      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>75</v>
       </c>
       <c r="B71" s="8">
-        <v>207</v>
+        <v>792.35</v>
       </c>
       <c r="C71" s="10">
-        <v>199.2</v>
+        <v>775.5</v>
       </c>
       <c r="D71" s="13"/>
       <c r="E71" s="5"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="5"/>
+      <c r="F71" s="16">
+        <v>207</v>
+      </c>
+      <c r="G71" s="5">
+        <v>199.2</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B72" s="8">
-        <v>2661.8</v>
+        <v>364.9</v>
       </c>
       <c r="C72" s="10">
-        <v>2599.25</v>
+        <v>358.25</v>
       </c>
       <c r="D72" s="13"/>
       <c r="E72" s="5"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="5"/>
+      <c r="F72" s="16">
+        <v>2661.8</v>
+      </c>
+      <c r="G72" s="5">
+        <v>2599.25</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B73" s="8">
-        <v>3215.9</v>
+        <v>2394.6</v>
       </c>
       <c r="C73" s="10">
-        <v>3135</v>
+        <v>2335</v>
       </c>
       <c r="D73" s="13"/>
       <c r="E73" s="5"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="5"/>
+      <c r="F73" s="16">
+        <v>3215.9</v>
+      </c>
+      <c r="G73" s="5">
+        <v>3135</v>
+      </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B74" s="8">
-        <v>1489.5</v>
+        <v>4386.3999999999996</v>
       </c>
       <c r="C74" s="10">
-        <v>1456.7</v>
+        <v>4289.8500000000004</v>
       </c>
       <c r="D74" s="13"/>
       <c r="E74" s="5"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="5"/>
+      <c r="F74" s="16">
+        <v>1489.5</v>
+      </c>
+      <c r="G74" s="5">
+        <v>1456.7</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B75" s="8">
-        <v>252.4</v>
+        <v>1013.4</v>
       </c>
       <c r="C75" s="10">
-        <v>241.2</v>
+        <v>991.35</v>
       </c>
       <c r="D75" s="13"/>
       <c r="E75" s="5"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="5"/>
+      <c r="F75" s="16">
+        <v>252.4</v>
+      </c>
+      <c r="G75" s="5">
+        <v>241.2</v>
+      </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B76" s="8">
-        <v>1199</v>
+        <v>354.5</v>
       </c>
       <c r="C76" s="10">
-        <v>1101</v>
+        <v>345.6</v>
       </c>
       <c r="D76" s="13"/>
       <c r="E76" s="5"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="5"/>
+      <c r="F76" s="16">
+        <v>1199</v>
+      </c>
+      <c r="G76" s="5">
+        <v>1101</v>
+      </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B77" s="8">
-        <v>1194.9000000000001</v>
+        <v>739.2</v>
       </c>
       <c r="C77" s="10">
-        <v>1143.9000000000001</v>
+        <v>714.6</v>
       </c>
       <c r="D77" s="13"/>
       <c r="E77" s="5"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="5"/>
+      <c r="F77" s="16">
+        <v>1194.9000000000001</v>
+      </c>
+      <c r="G77" s="5">
+        <v>1143.9000000000001</v>
+      </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B78" s="8">
-        <v>783.1</v>
+        <v>1533.9</v>
       </c>
       <c r="C78" s="10">
-        <v>760.9</v>
+        <v>1503.55</v>
       </c>
       <c r="D78" s="13"/>
       <c r="E78" s="5"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="5"/>
+      <c r="F78" s="16">
+        <v>783.1</v>
+      </c>
+      <c r="G78" s="5">
+        <v>760.9</v>
+      </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B79" s="8">
-        <v>4122.1499999999996</v>
+        <v>903.8</v>
       </c>
       <c r="C79" s="10">
-        <v>4010.05</v>
+        <v>885.5</v>
       </c>
       <c r="D79" s="13"/>
       <c r="E79" s="5"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="5"/>
+      <c r="F79" s="16">
+        <v>4122.1499999999996</v>
+      </c>
+      <c r="G79" s="5">
+        <v>4010.05</v>
+      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B80" s="8">
-        <v>790.2</v>
+        <v>4229.7</v>
       </c>
       <c r="C80" s="10">
-        <v>774.55</v>
+        <v>4097.6000000000004</v>
       </c>
       <c r="D80" s="13"/>
       <c r="E80" s="5"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="5"/>
+      <c r="F80" s="16">
+        <v>790.2</v>
+      </c>
+      <c r="G80" s="5">
+        <v>774.55</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B81" s="8">
-        <v>453.25</v>
+        <v>974.95</v>
       </c>
       <c r="C81" s="10">
-        <v>439.9</v>
+        <v>949.05</v>
       </c>
       <c r="D81" s="13"/>
       <c r="E81" s="5"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="5"/>
+      <c r="F81" s="16">
+        <v>453.25</v>
+      </c>
+      <c r="G81" s="5">
+        <v>439.9</v>
+      </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B82" s="8">
-        <v>1756</v>
+        <v>658.45</v>
       </c>
       <c r="C82" s="10">
-        <v>1721.2</v>
+        <v>638.25</v>
       </c>
       <c r="D82" s="13"/>
       <c r="E82" s="5"/>
-      <c r="F82" s="16"/>
-      <c r="G82" s="5"/>
+      <c r="F82" s="16">
+        <v>1756</v>
+      </c>
+      <c r="G82" s="5">
+        <v>1721.2</v>
+      </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B83" s="8">
-        <v>2065</v>
+        <v>1788.9</v>
       </c>
       <c r="C83" s="10">
-        <v>2013.2</v>
+        <v>1753.5</v>
       </c>
       <c r="D83" s="13"/>
       <c r="E83" s="5"/>
-      <c r="F83" s="16"/>
-      <c r="G83" s="5"/>
+      <c r="F83" s="16">
+        <v>2065</v>
+      </c>
+      <c r="G83" s="5">
+        <v>2013.2</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B84" s="8">
-        <v>403.1</v>
+        <v>3042.95</v>
       </c>
       <c r="C84" s="10">
-        <v>389.5</v>
+        <v>2970</v>
       </c>
       <c r="D84" s="13"/>
       <c r="E84" s="5"/>
-      <c r="F84" s="16"/>
-      <c r="G84" s="5"/>
+      <c r="F84" s="16">
+        <v>403.1</v>
+      </c>
+      <c r="G84" s="5">
+        <v>389.5</v>
+      </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>89</v>
       </c>
       <c r="B85" s="8">
-        <v>594.75</v>
+        <v>555.54999999999995</v>
       </c>
       <c r="C85" s="10">
-        <v>575.25</v>
+        <v>537.20000000000005</v>
       </c>
       <c r="D85" s="13"/>
       <c r="E85" s="5"/>
-      <c r="F85" s="16"/>
-      <c r="G85" s="5"/>
+      <c r="F85" s="16">
+        <v>594.75</v>
+      </c>
+      <c r="G85" s="5">
+        <v>575.25</v>
+      </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>90</v>
       </c>
       <c r="B86" s="8">
-        <v>5249.95</v>
+        <v>639.65</v>
       </c>
       <c r="C86" s="10">
-        <v>5170</v>
+        <v>627</v>
       </c>
       <c r="D86" s="13"/>
       <c r="E86" s="5"/>
-      <c r="F86" s="16"/>
-      <c r="G86" s="5"/>
+      <c r="F86" s="16">
+        <v>5249.95</v>
+      </c>
+      <c r="G86" s="5">
+        <v>5170</v>
+      </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>91</v>
       </c>
       <c r="B87" s="8">
-        <v>5437.85</v>
+        <v>6273.9</v>
       </c>
       <c r="C87" s="10">
-        <v>5242.2</v>
+        <v>6085.55</v>
       </c>
       <c r="D87" s="13"/>
       <c r="E87" s="5"/>
-      <c r="F87" s="16"/>
-      <c r="G87" s="5"/>
+      <c r="F87" s="16">
+        <v>5437.85</v>
+      </c>
+      <c r="G87" s="5">
+        <v>5242.2</v>
+      </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B88" s="8">
-        <v>1674</v>
+        <v>5440</v>
       </c>
       <c r="C88" s="10">
-        <v>1614</v>
+        <v>5220</v>
       </c>
       <c r="D88" s="13"/>
       <c r="E88" s="5"/>
-      <c r="F88" s="16"/>
-      <c r="G88" s="5"/>
+      <c r="F88" s="16">
+        <v>1674</v>
+      </c>
+      <c r="G88" s="5">
+        <v>1614</v>
+      </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>93</v>
       </c>
       <c r="B89" s="8">
-        <v>269.7</v>
+        <v>2021</v>
       </c>
       <c r="C89" s="10">
-        <v>260.10000000000002</v>
+        <v>1986</v>
       </c>
       <c r="D89" s="13"/>
       <c r="E89" s="5"/>
-      <c r="F89" s="16"/>
-      <c r="G89" s="5"/>
+      <c r="F89" s="16">
+        <v>269.7</v>
+      </c>
+      <c r="G89" s="5">
+        <v>260.10000000000002</v>
+      </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B90" s="8">
-        <v>167.35</v>
+        <v>276.10000000000002</v>
       </c>
       <c r="C90" s="10">
-        <v>161.65</v>
+        <v>269.85000000000002</v>
       </c>
       <c r="D90" s="13"/>
       <c r="E90" s="5"/>
-      <c r="F90" s="16"/>
-      <c r="G90" s="5"/>
+      <c r="F90" s="16">
+        <v>167.35</v>
+      </c>
+      <c r="G90" s="5">
+        <v>161.65</v>
+      </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B91" s="8">
-        <v>509.65</v>
+        <v>157.9</v>
       </c>
       <c r="C91" s="10">
-        <v>496.5</v>
+        <v>154.01</v>
       </c>
       <c r="D91" s="13"/>
       <c r="E91" s="5"/>
-      <c r="F91" s="16"/>
-      <c r="G91" s="5"/>
+      <c r="F91" s="16">
+        <v>509.65</v>
+      </c>
+      <c r="G91" s="5">
+        <v>496.5</v>
+      </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B92" s="8">
-        <v>1162</v>
+        <v>664.1</v>
       </c>
       <c r="C92" s="10">
-        <v>1108.45</v>
+        <v>642.79999999999995</v>
       </c>
       <c r="D92" s="13"/>
       <c r="E92" s="5"/>
-      <c r="F92" s="16"/>
-      <c r="G92" s="5"/>
+      <c r="F92" s="16">
+        <v>1162</v>
+      </c>
+      <c r="G92" s="5">
+        <v>1108.45</v>
+      </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
         <v>97</v>
       </c>
       <c r="B93" s="8">
-        <v>3277.45</v>
+        <v>1522.75</v>
       </c>
       <c r="C93" s="10">
-        <v>3075.25</v>
+        <v>1495.45</v>
       </c>
       <c r="D93" s="13"/>
       <c r="E93" s="5"/>
-      <c r="F93" s="16"/>
-      <c r="G93" s="5"/>
+      <c r="F93" s="16">
+        <v>3277.45</v>
+      </c>
+      <c r="G93" s="5">
+        <v>3075.25</v>
+      </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
         <v>98</v>
       </c>
       <c r="B94" s="8">
-        <v>1627.95</v>
+        <v>6224</v>
       </c>
       <c r="C94" s="10">
-        <v>1580.1</v>
+        <v>6062.25</v>
       </c>
       <c r="D94" s="13"/>
       <c r="E94" s="5"/>
-      <c r="F94" s="16"/>
-      <c r="G94" s="5"/>
+      <c r="F94" s="16">
+        <v>1627.95</v>
+      </c>
+      <c r="G94" s="5">
+        <v>1580.1</v>
+      </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>99</v>
       </c>
       <c r="B95" s="8">
-        <v>994</v>
+        <v>2186.6999999999998</v>
       </c>
       <c r="C95" s="10">
-        <v>952.9</v>
+        <v>2128.4</v>
       </c>
       <c r="D95" s="13"/>
       <c r="E95" s="5"/>
-      <c r="F95" s="16"/>
-      <c r="G95" s="5"/>
+      <c r="F95" s="16">
+        <v>994</v>
+      </c>
+      <c r="G95" s="5">
+        <v>952.9</v>
+      </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B96" s="8">
-        <v>1279.6500000000001</v>
+        <v>1197.75</v>
       </c>
       <c r="C96" s="10">
-        <v>1243</v>
+        <v>1093.8499999999999</v>
       </c>
       <c r="D96" s="13"/>
       <c r="E96" s="5"/>
-      <c r="F96" s="16"/>
-      <c r="G96" s="5"/>
+      <c r="F96" s="16">
+        <v>1279.6500000000001</v>
+      </c>
+      <c r="G96" s="5">
+        <v>1243</v>
+      </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
         <v>101</v>
       </c>
       <c r="B97" s="8">
-        <v>2502</v>
+        <v>1198.6500000000001</v>
       </c>
       <c r="C97" s="10">
-        <v>2455.85</v>
+        <v>1167</v>
       </c>
       <c r="D97" s="13"/>
       <c r="E97" s="5"/>
-      <c r="F97" s="16"/>
-      <c r="G97" s="5"/>
+      <c r="F97" s="16">
+        <v>2502</v>
+      </c>
+      <c r="G97" s="5">
+        <v>2455.85</v>
+      </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>102</v>
       </c>
       <c r="B98" s="8">
-        <v>1368.9</v>
+        <v>3026.85</v>
       </c>
       <c r="C98" s="10">
-        <v>1328.85</v>
+        <v>2938.65</v>
       </c>
       <c r="D98" s="13"/>
       <c r="E98" s="5"/>
-      <c r="F98" s="16"/>
-      <c r="G98" s="5"/>
+      <c r="F98" s="16">
+        <v>1368.9</v>
+      </c>
+      <c r="G98" s="5">
+        <v>1328.85</v>
+      </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>103</v>
       </c>
       <c r="B99" s="8">
-        <v>488.7</v>
+        <v>1951.1</v>
       </c>
       <c r="C99" s="10">
-        <v>450.5</v>
+        <v>1895</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="5"/>
-      <c r="F99" s="16"/>
-      <c r="G99" s="5"/>
+      <c r="F99" s="16">
+        <v>488.7</v>
+      </c>
+      <c r="G99" s="5">
+        <v>450.5</v>
+      </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>104</v>
       </c>
       <c r="B100" s="8">
-        <v>5280</v>
+        <v>706.95</v>
       </c>
       <c r="C100" s="10">
-        <v>5161.3</v>
+        <v>688.05</v>
       </c>
       <c r="D100" s="13"/>
       <c r="E100" s="5"/>
-      <c r="F100" s="16"/>
-      <c r="G100" s="5"/>
+      <c r="F100" s="16">
+        <v>5280</v>
+      </c>
+      <c r="G100" s="5">
+        <v>5161.3</v>
+      </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>105</v>
       </c>
       <c r="B101" s="8">
-        <v>3010.05</v>
+        <v>8404.65</v>
       </c>
       <c r="C101" s="10">
-        <v>2964.3</v>
+        <v>8176</v>
       </c>
       <c r="D101" s="13"/>
       <c r="E101" s="5"/>
-      <c r="F101" s="16"/>
-      <c r="G101" s="5"/>
+      <c r="F101" s="16">
+        <v>3010.05</v>
+      </c>
+      <c r="G101" s="5">
+        <v>2964.3</v>
+      </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>106</v>
       </c>
       <c r="B102" s="8">
-        <v>204.5</v>
+        <v>3535.4</v>
       </c>
       <c r="C102" s="10">
-        <v>190.35</v>
+        <v>3452.35</v>
       </c>
       <c r="D102" s="13"/>
       <c r="E102" s="5"/>
-      <c r="F102" s="16"/>
-      <c r="G102" s="5"/>
+      <c r="F102" s="16">
+        <v>204.5</v>
+      </c>
+      <c r="G102" s="5">
+        <v>190.35</v>
+      </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
         <v>107</v>
       </c>
       <c r="B103" s="8">
-        <v>326.05</v>
+        <v>230.8</v>
       </c>
       <c r="C103" s="10">
-        <v>305.75</v>
+        <v>226.85</v>
       </c>
       <c r="D103" s="13"/>
       <c r="E103" s="5"/>
-      <c r="F103" s="16"/>
-      <c r="G103" s="5"/>
+      <c r="F103" s="16">
+        <v>326.05</v>
+      </c>
+      <c r="G103" s="5">
+        <v>305.75</v>
+      </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>108</v>
       </c>
       <c r="B104" s="8">
-        <v>1343.95</v>
+        <v>371.85</v>
       </c>
       <c r="C104" s="10">
-        <v>1297.25</v>
+        <v>359.6</v>
       </c>
       <c r="D104" s="13"/>
       <c r="E104" s="5"/>
-      <c r="F104" s="16"/>
-      <c r="G104" s="5"/>
+      <c r="F104" s="16">
+        <v>1343.95</v>
+      </c>
+      <c r="G104" s="5">
+        <v>1297.25</v>
+      </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>109</v>
       </c>
       <c r="B105" s="8">
-        <v>266.39999999999998</v>
+        <v>2025.5</v>
       </c>
       <c r="C105" s="10">
-        <v>248.9</v>
+        <v>1972.35</v>
       </c>
       <c r="D105" s="13"/>
       <c r="E105" s="5"/>
-      <c r="F105" s="16"/>
-      <c r="G105" s="5"/>
+      <c r="F105" s="16">
+        <v>266.39999999999998</v>
+      </c>
+      <c r="G105" s="5">
+        <v>248.9</v>
+      </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>110</v>
       </c>
       <c r="B106" s="8">
-        <v>843.5</v>
+        <v>257.39999999999998</v>
       </c>
       <c r="C106" s="10">
-        <v>814.8</v>
+        <v>251.2</v>
       </c>
       <c r="D106" s="13"/>
       <c r="E106" s="5"/>
-      <c r="F106" s="16"/>
-      <c r="G106" s="5"/>
+      <c r="F106" s="16">
+        <v>843.5</v>
+      </c>
+      <c r="G106" s="5">
+        <v>814.8</v>
+      </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
         <v>111</v>
       </c>
       <c r="B107" s="8">
-        <v>8454.85</v>
+        <v>1205.3</v>
       </c>
       <c r="C107" s="10">
-        <v>8180</v>
+        <v>1171.8499999999999</v>
       </c>
       <c r="D107" s="13"/>
       <c r="E107" s="5"/>
-      <c r="F107" s="16"/>
-      <c r="G107" s="5"/>
+      <c r="F107" s="16">
+        <v>8454.85</v>
+      </c>
+      <c r="G107" s="5">
+        <v>8180</v>
+      </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
         <v>112</v>
       </c>
       <c r="B108" s="8">
-        <v>269.60000000000002</v>
+        <v>5938.8</v>
       </c>
       <c r="C108" s="10">
-        <v>258.05</v>
+        <v>5802.05</v>
       </c>
       <c r="D108" s="13"/>
       <c r="E108" s="5"/>
-      <c r="F108" s="16"/>
-      <c r="G108" s="5"/>
+      <c r="F108" s="16">
+        <v>269.60000000000002</v>
+      </c>
+      <c r="G108" s="5">
+        <v>258.05</v>
+      </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
         <v>113</v>
       </c>
       <c r="B109" s="8">
-        <v>2894</v>
+        <v>330.3</v>
       </c>
       <c r="C109" s="10">
-        <v>2819</v>
+        <v>326.05</v>
       </c>
       <c r="D109" s="13"/>
       <c r="E109" s="5"/>
-      <c r="F109" s="16"/>
-      <c r="G109" s="5"/>
+      <c r="F109" s="16">
+        <v>2894</v>
+      </c>
+      <c r="G109" s="5">
+        <v>2819</v>
+      </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
         <v>114</v>
       </c>
       <c r="B110" s="8">
-        <v>4918.05</v>
+        <v>3063</v>
       </c>
       <c r="C110" s="10">
-        <v>4775</v>
+        <v>3001.15</v>
       </c>
       <c r="D110" s="13"/>
       <c r="E110" s="5"/>
-      <c r="F110" s="16"/>
-      <c r="G110" s="5"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F110" s="16">
+        <v>4918.05</v>
+      </c>
+      <c r="G110" s="5">
+        <v>4775</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B111" s="8">
-        <v>272</v>
-      </c>
-      <c r="C111" s="10">
-        <v>257.64999999999998</v>
+      <c r="B111" s="18">
+        <v>7165.25</v>
+      </c>
+      <c r="C111" s="11">
+        <v>7039.3</v>
       </c>
       <c r="D111" s="13"/>
       <c r="E111" s="5"/>
-      <c r="F111" s="16"/>
-      <c r="G111" s="5"/>
+      <c r="F111" s="16">
+        <v>272</v>
+      </c>
+      <c r="G111" s="5">
+        <v>257.64999999999998</v>
+      </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B112" s="8">
-        <v>162.30000000000001</v>
-      </c>
-      <c r="C112" s="10">
-        <v>156.35</v>
+      <c r="B112">
+        <v>341.75</v>
+      </c>
+      <c r="C112">
+        <v>332.2</v>
       </c>
       <c r="D112" s="13"/>
       <c r="E112" s="5"/>
-      <c r="F112" s="16"/>
-      <c r="G112" s="5"/>
+      <c r="F112" s="16">
+        <v>162.30000000000001</v>
+      </c>
+      <c r="G112" s="5">
+        <v>156.35</v>
+      </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B113" s="8">
-        <v>809</v>
-      </c>
-      <c r="C113" s="10">
-        <v>792.7</v>
+      <c r="B113">
+        <v>153.59</v>
+      </c>
+      <c r="C113">
+        <v>151.06</v>
       </c>
       <c r="D113" s="13"/>
       <c r="E113" s="5"/>
-      <c r="F113" s="16"/>
-      <c r="G113" s="5"/>
+      <c r="F113" s="16">
+        <v>809</v>
+      </c>
+      <c r="G113" s="5">
+        <v>792.7</v>
+      </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B114" s="8">
-        <v>230.65</v>
-      </c>
-      <c r="C114" s="10">
-        <v>222.25</v>
+      <c r="B114">
+        <v>980.9</v>
+      </c>
+      <c r="C114">
+        <v>969.3</v>
       </c>
       <c r="D114" s="13"/>
       <c r="E114" s="5"/>
-      <c r="F114" s="16"/>
-      <c r="G114" s="5"/>
+      <c r="F114" s="16">
+        <v>230.65</v>
+      </c>
+      <c r="G114" s="5">
+        <v>222.25</v>
+      </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B115" s="8">
-        <v>466.5</v>
-      </c>
-      <c r="C115" s="10">
-        <v>430.35</v>
+      <c r="B115">
+        <v>161.19</v>
+      </c>
+      <c r="C115">
+        <v>156.9</v>
       </c>
       <c r="D115" s="13"/>
       <c r="E115" s="5"/>
-      <c r="F115" s="16"/>
-      <c r="G115" s="5"/>
+      <c r="F115" s="16">
+        <v>466.5</v>
+      </c>
+      <c r="G115" s="5">
+        <v>430.35</v>
+      </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B116" s="8">
-        <v>704.65</v>
-      </c>
-      <c r="C116" s="10">
-        <v>696</v>
+      <c r="B116">
+        <v>535.75</v>
+      </c>
+      <c r="C116">
+        <v>524.4</v>
       </c>
       <c r="D116" s="13"/>
       <c r="E116" s="5"/>
-      <c r="F116" s="16"/>
-      <c r="G116" s="5"/>
+      <c r="F116" s="16">
+        <v>704.65</v>
+      </c>
+      <c r="G116" s="5">
+        <v>696</v>
+      </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B117" s="8">
-        <v>1504.95</v>
-      </c>
-      <c r="C117" s="10">
-        <v>1481.1</v>
+      <c r="B117">
+        <v>718</v>
+      </c>
+      <c r="C117">
+        <v>703.5</v>
       </c>
       <c r="D117" s="13"/>
       <c r="E117" s="5"/>
-      <c r="F117" s="16"/>
-      <c r="G117" s="5"/>
+      <c r="F117" s="16">
+        <v>1504.95</v>
+      </c>
+      <c r="G117" s="5">
+        <v>1481.1</v>
+      </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B118" s="8">
-        <v>4820.6000000000004</v>
-      </c>
-      <c r="C118" s="10">
-        <v>4682.1000000000004</v>
+      <c r="B118">
+        <v>1519.7</v>
+      </c>
+      <c r="C118">
+        <v>1403</v>
       </c>
       <c r="D118" s="13"/>
       <c r="E118" s="5"/>
-      <c r="F118" s="16"/>
-      <c r="G118" s="5"/>
+      <c r="F118" s="16">
+        <v>4820.6000000000004</v>
+      </c>
+      <c r="G118" s="5">
+        <v>4682.1000000000004</v>
+      </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B119" s="8">
-        <v>2449.9</v>
-      </c>
-      <c r="C119" s="10">
-        <v>2404.4</v>
+      <c r="B119">
+        <v>7598.35</v>
+      </c>
+      <c r="C119">
+        <v>7397.3</v>
       </c>
       <c r="D119" s="13"/>
       <c r="E119" s="5"/>
-      <c r="F119" s="16"/>
-      <c r="G119" s="5"/>
+      <c r="F119" s="16">
+        <v>2449.9</v>
+      </c>
+      <c r="G119" s="5">
+        <v>2404.4</v>
+      </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B120" s="8">
-        <v>799.2</v>
-      </c>
-      <c r="C120" s="10">
-        <v>766.85</v>
+      <c r="B120">
+        <v>2311.4499999999998</v>
+      </c>
+      <c r="C120">
+        <v>2254.5</v>
       </c>
       <c r="D120" s="13"/>
       <c r="E120" s="5"/>
-      <c r="F120" s="16"/>
-      <c r="G120" s="5"/>
+      <c r="F120" s="16">
+        <v>799.2</v>
+      </c>
+      <c r="G120" s="5">
+        <v>766.85</v>
+      </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B121" s="8">
-        <v>1573.5</v>
-      </c>
-      <c r="C121" s="10">
-        <v>1541.2</v>
+      <c r="B121">
+        <v>1607.6</v>
+      </c>
+      <c r="C121">
+        <v>1526.65</v>
       </c>
       <c r="D121" s="13"/>
       <c r="E121" s="5"/>
-      <c r="F121" s="16"/>
-      <c r="G121" s="5"/>
+      <c r="F121" s="16">
+        <v>1573.5</v>
+      </c>
+      <c r="G121" s="5">
+        <v>1541.2</v>
+      </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B122" s="8">
-        <v>687.9</v>
-      </c>
-      <c r="C122" s="10">
-        <v>671.9</v>
+      <c r="B122">
+        <v>1760.7</v>
+      </c>
+      <c r="C122">
+        <v>1723.4</v>
       </c>
       <c r="D122" s="13"/>
       <c r="E122" s="5"/>
-      <c r="F122" s="16"/>
-      <c r="G122" s="5"/>
+      <c r="F122" s="16">
+        <v>687.9</v>
+      </c>
+      <c r="G122" s="5">
+        <v>671.9</v>
+      </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B123" s="8">
-        <v>1954.6</v>
-      </c>
-      <c r="C123" s="10">
-        <v>1896.55</v>
+      <c r="B123">
+        <v>921</v>
+      </c>
+      <c r="C123">
+        <v>901.6</v>
       </c>
       <c r="D123" s="13"/>
       <c r="E123" s="5"/>
-      <c r="F123" s="16"/>
-      <c r="G123" s="5"/>
+      <c r="F123" s="16">
+        <v>1954.6</v>
+      </c>
+      <c r="G123" s="5">
+        <v>1896.55</v>
+      </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B124" s="8">
-        <v>979.75</v>
-      </c>
-      <c r="C124" s="10">
-        <v>940</v>
+      <c r="B124">
+        <v>1765.35</v>
+      </c>
+      <c r="C124">
+        <v>1728.15</v>
       </c>
       <c r="D124" s="13"/>
       <c r="E124" s="5"/>
-      <c r="F124" s="16"/>
-      <c r="G124" s="5"/>
+      <c r="F124" s="16">
+        <v>979.75</v>
+      </c>
+      <c r="G124" s="5">
+        <v>940</v>
+      </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B125" s="8">
-        <v>1293</v>
-      </c>
-      <c r="C125" s="10">
-        <v>1268.5</v>
+      <c r="B125">
+        <v>792.55</v>
+      </c>
+      <c r="C125">
+        <v>778</v>
       </c>
       <c r="D125" s="13"/>
       <c r="E125" s="5"/>
-      <c r="F125" s="16"/>
-      <c r="G125" s="5"/>
+      <c r="F125" s="16">
+        <v>1293</v>
+      </c>
+      <c r="G125" s="5">
+        <v>1268.5</v>
+      </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B126" s="8">
-        <v>2711.1</v>
-      </c>
-      <c r="C126" s="10">
-        <v>2577</v>
+      <c r="B126">
+        <v>4339.95</v>
+      </c>
+      <c r="C126">
+        <v>4233</v>
       </c>
       <c r="D126" s="13"/>
       <c r="E126" s="5"/>
-      <c r="F126" s="16"/>
-      <c r="G126" s="5"/>
+      <c r="F126" s="16">
+        <v>2711.1</v>
+      </c>
+      <c r="G126" s="5">
+        <v>2577</v>
+      </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B127" s="8">
-        <v>1185</v>
-      </c>
-      <c r="C127" s="10">
-        <v>1115.45</v>
+      <c r="B127">
+        <v>1760</v>
+      </c>
+      <c r="C127">
+        <v>1706.8</v>
       </c>
       <c r="D127" s="13"/>
       <c r="E127" s="5"/>
-      <c r="F127" s="16"/>
-      <c r="G127" s="5"/>
+      <c r="F127" s="16">
+        <v>1185</v>
+      </c>
+      <c r="G127" s="5">
+        <v>1115.45</v>
+      </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B128" s="8">
-        <v>4145</v>
-      </c>
-      <c r="C128" s="10">
-        <v>3981.25</v>
+      <c r="B128">
+        <v>3305</v>
+      </c>
+      <c r="C128">
+        <v>3200.35</v>
       </c>
       <c r="D128" s="13"/>
       <c r="E128" s="5"/>
-      <c r="F128" s="16"/>
-      <c r="G128" s="5"/>
+      <c r="F128" s="16">
+        <v>4145</v>
+      </c>
+      <c r="G128" s="5">
+        <v>3981.25</v>
+      </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B129" s="8">
-        <v>2159</v>
-      </c>
-      <c r="C129" s="10">
-        <v>2054.9499999999998</v>
+      <c r="B129">
+        <v>3237.95</v>
+      </c>
+      <c r="C129">
+        <v>3172.45</v>
       </c>
       <c r="D129" s="13"/>
       <c r="E129" s="5"/>
-      <c r="F129" s="16"/>
-      <c r="G129" s="5"/>
+      <c r="F129" s="16">
+        <v>2159</v>
+      </c>
+      <c r="G129" s="5">
+        <v>2054.9499999999998</v>
+      </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B130" s="8">
-        <v>1745.95</v>
-      </c>
-      <c r="C130" s="10">
-        <v>1696.25</v>
+      <c r="B130">
+        <v>1553</v>
+      </c>
+      <c r="C130">
+        <v>1502.75</v>
       </c>
       <c r="D130" s="13"/>
       <c r="E130" s="5"/>
-      <c r="F130" s="16"/>
-      <c r="G130" s="5"/>
+      <c r="F130" s="16">
+        <v>1745.95</v>
+      </c>
+      <c r="G130" s="5">
+        <v>1696.25</v>
+      </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B131" s="8">
-        <v>9750.9</v>
-      </c>
-      <c r="C131" s="10">
-        <v>9543.7999999999993</v>
+      <c r="B131">
+        <v>6886.45</v>
+      </c>
+      <c r="C131">
+        <v>6716.05</v>
       </c>
       <c r="D131" s="13"/>
       <c r="E131" s="5"/>
-      <c r="F131" s="16"/>
-      <c r="G131" s="5"/>
+      <c r="F131" s="16">
+        <v>9750.9</v>
+      </c>
+      <c r="G131" s="5">
+        <v>9543.7999999999993</v>
+      </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B132" s="8">
-        <v>477.5</v>
-      </c>
-      <c r="C132" s="10">
-        <v>459.45</v>
+      <c r="B132">
+        <v>2459.1999999999998</v>
+      </c>
+      <c r="C132">
+        <v>2410</v>
       </c>
       <c r="D132" s="13"/>
       <c r="E132" s="5"/>
-      <c r="F132" s="16"/>
-      <c r="G132" s="5"/>
+      <c r="F132" s="16">
+        <v>477.5</v>
+      </c>
+      <c r="G132" s="5">
+        <v>459.45</v>
+      </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B133" s="8">
-        <v>266</v>
-      </c>
-      <c r="C133" s="10">
-        <v>255.15</v>
+      <c r="B133">
+        <v>1955.85</v>
+      </c>
+      <c r="C133">
+        <v>1921.6</v>
       </c>
       <c r="D133" s="13"/>
       <c r="E133" s="5"/>
-      <c r="F133" s="16"/>
-      <c r="G133" s="5"/>
+      <c r="F133" s="16">
+        <v>266</v>
+      </c>
+      <c r="G133" s="5">
+        <v>255.15</v>
+      </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B134" s="8">
-        <v>1073.6500000000001</v>
-      </c>
-      <c r="C134" s="10">
-        <v>1050.05</v>
+      <c r="B134">
+        <v>11190</v>
+      </c>
+      <c r="C134">
+        <v>10957.6</v>
       </c>
       <c r="D134" s="13"/>
       <c r="E134" s="5"/>
-      <c r="F134" s="16"/>
-      <c r="G134" s="5"/>
+      <c r="F134" s="16">
+        <v>1073.6500000000001</v>
+      </c>
+      <c r="G134" s="5">
+        <v>1050.05</v>
+      </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B135" s="8">
-        <v>149.1</v>
-      </c>
-      <c r="C135" s="10">
-        <v>141</v>
+      <c r="B135">
+        <v>557.15</v>
+      </c>
+      <c r="C135">
+        <v>545</v>
       </c>
       <c r="D135" s="13"/>
       <c r="E135" s="5"/>
-      <c r="F135" s="16"/>
-      <c r="G135" s="5"/>
+      <c r="F135" s="16">
+        <v>149.1</v>
+      </c>
+      <c r="G135" s="5">
+        <v>141</v>
+      </c>
     </row>
     <row r="136" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B136" s="8">
-        <v>994.65</v>
-      </c>
-      <c r="C136" s="10">
-        <v>971.25</v>
+      <c r="B136">
+        <v>456.35</v>
+      </c>
+      <c r="C136">
+        <v>448.9</v>
       </c>
       <c r="D136" s="14"/>
       <c r="E136" s="6"/>
-      <c r="F136" s="17"/>
-      <c r="G136" s="6"/>
+      <c r="F136" s="17">
+        <v>994.65</v>
+      </c>
+      <c r="G136" s="6">
+        <v>971.25</v>
+      </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B137" s="8"/>
-      <c r="C137" s="10"/>
+      <c r="B137">
+        <v>1677.9</v>
+      </c>
+      <c r="C137">
+        <v>1637.1</v>
+      </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B138" s="8"/>
-      <c r="C138" s="10"/>
+      <c r="B138">
+        <v>124.79</v>
+      </c>
+      <c r="C138">
+        <v>122.07</v>
+      </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B139" s="8"/>
-      <c r="C139" s="10"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B140" s="8"/>
-      <c r="C140" s="10"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B141" s="8"/>
-      <c r="C141" s="10"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B142" s="8"/>
-      <c r="C142" s="10"/>
-    </row>
-    <row r="143" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B143" s="18"/>
-      <c r="C143" s="11"/>
-    </row>
+      <c r="B139">
+        <v>954.95</v>
+      </c>
+      <c r="C139">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
